--- a/results/Int Task Remove ACC -0.7/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_8_permute.xlsx
@@ -440,477 +440,477 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6446958882882002</v>
+        <v>0.6184454651110034</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6438671590064323</v>
+        <v>0.6126485482840819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6438671590064323</v>
+        <v>0.6126089354083267</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6442226278518652</v>
+        <v>0.6156090436020842</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.632184676273807</v>
+        <v>0.6048699406330382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5702228093381683</v>
+        <v>0.6066013897662665</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5732885318107098</v>
+        <v>0.5705313360533011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5757747196560137</v>
+        <v>0.582888284710128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.538443336137064</v>
+        <v>0.5823357985222827</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.538443336137064</v>
+        <v>0.5834397238616097</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5399111066127327</v>
+        <v>0.5731759754016257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5521471225695669</v>
+        <v>0.5760176320923626</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5163136990747689</v>
+        <v>0.5754651459045173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5160364089444827</v>
+        <v>0.576372053901432</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5047907148815278</v>
+        <v>0.5774332252559131</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4994190693242777</v>
+        <v>0.5774332252559131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5031301152089012</v>
+        <v>0.5819291994010952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4960666333941778</v>
+        <v>0.5819291994010952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5015497883241484</v>
+        <v>0.5936961430670488</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4870308840826042</v>
+        <v>0.592546322633785</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4882943079613155</v>
+        <v>0.5902602932399843</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4927923761792247</v>
+        <v>0.5968536557274634</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4837899575252248</v>
+        <v>0.5786184704194777</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.477075662337753</v>
+        <v>0.5782609075013175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4887633802521962</v>
+        <v>0.5312672979132566</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4863574651947662</v>
+        <v>0.5094440934933671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4864366909462765</v>
+        <v>0.507666749266202</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4871872415128978</v>
+        <v>0.5265764004983893</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4615570128750571</v>
+        <v>0.5432239296670773</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4724128603986416</v>
+        <v>0.5134261472900954</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4504259692939135</v>
+        <v>0.5239296670773376</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4371277349462347</v>
+        <v>0.4878732248370986</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.442656784970142</v>
+        <v>0.4856955637069276</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4574196486843988</v>
+        <v>0.4897557962188027</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4531550695755664</v>
+        <v>0.4866399905068703</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4528788264816437</v>
+        <v>0.4815445880435427</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4784964906831214</v>
+        <v>0.4854505571978515</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4454066514730056</v>
+        <v>0.4717561940926208</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4514787643574861</v>
+        <v>0.4711630479926567</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4479387344122461</v>
+        <v>0.4483755230819166</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4479387344122461</v>
+        <v>0.404979181426971</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4307292957284407</v>
+        <v>0.4263854908680978</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4307292957284407</v>
+        <v>0.4409534313126695</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4167190766535322</v>
+        <v>0.430290412986043</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4427276344307438</v>
+        <v>0.430290412986043</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4267826666620132</v>
+        <v>0.4214902468562733</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4120416162053309</v>
+        <v>0.4270130146619993</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3881428367007186</v>
+        <v>0.4362134976947749</v>
       </c>
     </row>
     <row r="50">
@@ -920,397 +920,397 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3881428367007186</v>
+        <v>0.4362134976947749</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4221071257804784</v>
+        <v>0.4366867581311099</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4228972892228547</v>
+        <v>0.4505479490302698</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4122864482083463</v>
+        <v>0.4022136093786537</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4154992792899698</v>
+        <v>0.3842181953979262</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4165000715474848</v>
+        <v>0.3786099196225085</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4141274871476286</v>
+        <v>0.4138336189415859</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4207198025987443</v>
+        <v>0.4145445566324519</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4321436673495671</v>
+        <v>0.4694293302806406</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4324199104434897</v>
+        <v>0.4694293302806406</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4381438837370822</v>
+        <v>0.4764729184044562</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.429987993983031</v>
+        <v>0.4826118671101447</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.429987993983031</v>
+        <v>0.4655036419414846</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4139512360264272</v>
+        <v>0.4555287010117862</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4233049353804058</v>
+        <v>0.4904323562157314</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4242055611591391</v>
+        <v>0.4869141395280658</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3991904663848975</v>
+        <v>0.4869141395280658</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4064322933935496</v>
+        <v>0.4852160210524112</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.3953429567608883</v>
+        <v>0.4845050833615452</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3997138100606234</v>
+        <v>0.4680608537534509</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4068764113177651</v>
+        <v>0.4546896758724431</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4065605553480872</v>
+        <v>0.4303895324284612</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4230789500319346</v>
+        <v>0.398270121421317</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4661824705172011</v>
+        <v>0.4039159159997627</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4690230801715744</v>
+        <v>0.4295346272376039</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4705596060351176</v>
+        <v>0.4295346272376039</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4816916966526247</v>
+        <v>0.4777178446407443</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4873081742128904</v>
+        <v>0.4903178802399807</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5002423889181671</v>
+        <v>0.4887771662309832</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4880438917643609</v>
+        <v>0.4869205962523079</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5113170670417383</v>
+        <v>0.4688386272655249</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.51265971667196</v>
+        <v>0.46966945062002</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4918486474035243</v>
+        <v>0.4695411886654823</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4635697657779655</v>
+        <v>0.4666161180777809</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4763333135559798</v>
+        <v>0.4618730433507955</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4947623750972872</v>
+        <v>0.462900884047703</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5027723777846804</v>
+        <v>0.4969581848577601</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5007582288332874</v>
+        <v>0.4996424370818399</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5011533105544755</v>
+        <v>0.499917633139399</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5055908251693582</v>
+        <v>0.4996830969939586</v>
       </c>
     </row>
     <row r="90">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.507315992084405</v>
+        <v>0.4987355290849251</v>
       </c>
     </row>
   </sheetData>
